--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_08-07-2025.xlsx
@@ -1053,7 +1053,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£24.68</t>
+          <t>Error: 'NoneType' object has no attribute 'find'</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1120,17 +1120,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>£23.86</t>
+          <t>£23.50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>£23.86</t>
+          <t>£23.50</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>£23.49</t>
+          <t>£23.50</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1217,17 +1217,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£26.78</t>
+          <t>£26.50</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£26.78</t>
+          <t>£26.50</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£26.78</t>
+          <t>£26.50</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1314,17 +1314,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£29.28</t>
+          <t>£29.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£29.28</t>
+          <t>£29.00</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£29.28</t>
+          <t>£29.00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1411,17 +1411,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£29.25</t>
+          <t>£29.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£29.25</t>
+          <t>£29.00</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£29.25</t>
+          <t>£29.00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1508,17 +1508,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£36.90</t>
+          <t>£36.50</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£36.90</t>
+          <t>£36.50</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£36.90</t>
+          <t>£36.50</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1702,17 +1702,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£42.78</t>
+          <t>£42.50</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£42.78</t>
+          <t>£42.50</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£42.78</t>
+          <t>£42.50</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1896,17 +1896,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£43.58</t>
+          <t>£43.50</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£43.58</t>
+          <t>£43.50</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£43.58</t>
+          <t>£43.50</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2187,17 +2187,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£31.90</t>
+          <t>£29.40</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>£31.90</t>
+          <t>£29.40</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>£29.79</t>
+          <t>£29.40</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2284,17 +2284,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£39.91</t>
+          <t>£36.20</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>£39.91</t>
+          <t>£36.20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>£36.73</t>
+          <t>£36.20</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>£42.90</t>
+          <t>£33.35</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>£42.90</t>
+          <t>£33.35</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>£39.88</t>
+          <t>£33.35</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2478,17 +2478,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>£52.00</t>
+          <t>£43.89</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>£52.00</t>
+          <t>£43.89</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>£43.89</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2575,17 +2575,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>£45.50</t>
+          <t>£44.60</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>£45.50</t>
+          <t>£44.60</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>£45.19</t>
+          <t>£44.60</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>£45.00</t>
+          <t>£44.20</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>£45.00</t>
+          <t>£44.20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>£44.78</t>
+          <t>£44.20</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>£1,200.00</t>
+          <t>£1,160.00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>£1,200.00</t>
+          <t>£1,160.00</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>£1,173.28</t>
+          <t>£1,160.00</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
